--- a/data/trans_orig/IQ39A-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ39A-Estudios-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adulto según el número de horas que trabaja habitualmente a la semana</t>
+          <t>Adulto según el número de horas que trabaja habitualmente a la semana (tasa de respuesta: 97,26%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>36,87; 43,82</t>
+          <t>36,7; 43,68</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>33,6; 41,0</t>
+          <t>33,68; 41,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22,66; 38,19</t>
+          <t>23,09; 38,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>32,19; 40,1</t>
+          <t>31,93; 40,13</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>33,17; 40,0</t>
+          <t>33,34; 39,84</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,22; 39,79</t>
+          <t>32,5; 39,67</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,63; 44,16</t>
+          <t>34,8; 43,78</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>29,49; 38,74</t>
+          <t>29,87; 38,88</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>35,85; 40,88</t>
+          <t>36,05; 41,1</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>34,2; 39,71</t>
+          <t>34,42; 39,9</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32,22; 40,43</t>
+          <t>31,98; 40,28</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>32,44; 38,62</t>
+          <t>32,04; 38,41</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>39,27; 41,42</t>
+          <t>39,26; 41,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>35,72; 38,22</t>
+          <t>35,65; 38,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36,31; 38,67</t>
+          <t>36,16; 38,66</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36,48; 38,48</t>
+          <t>36,52; 38,56</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>38,95; 40,87</t>
+          <t>39,0; 40,79</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,47; 39,32</t>
+          <t>36,36; 39,21</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,2; 38,78</t>
+          <t>36,18; 38,81</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>37,37; 39,69</t>
+          <t>37,44; 39,65</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>39,48; 40,93</t>
+          <t>39,37; 40,81</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36,51; 38,36</t>
+          <t>36,44; 38,29</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36,69; 38,47</t>
+          <t>36,61; 38,41</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>37,38; 38,81</t>
+          <t>37,27; 38,81</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>36,44; 38,86</t>
+          <t>36,39; 38,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>37,12; 39,89</t>
+          <t>37,01; 39,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>35,21; 38,34</t>
+          <t>35,31; 38,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>35,75; 38,4</t>
+          <t>35,89; 38,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>36,1; 38,59</t>
+          <t>36,0; 38,54</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>36,91; 39,75</t>
+          <t>37,04; 39,65</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>36,15; 38,62</t>
+          <t>36,2; 38,64</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>35,33; 37,58</t>
+          <t>35,38; 37,57</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>36,64; 38,33</t>
+          <t>36,61; 38,34</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>37,38; 39,27</t>
+          <t>37,36; 39,34</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>36,21; 38,12</t>
+          <t>36,19; 38,1</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>36,03; 37,62</t>
+          <t>36,0; 37,71</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>38,55; 40,25</t>
+          <t>38,57; 40,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>36,54; 38,37</t>
+          <t>36,62; 38,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>36,0; 37,93</t>
+          <t>36,14; 38,08</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>36,57; 38,12</t>
+          <t>36,56; 38,19</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>38,13; 39,72</t>
+          <t>38,24; 39,72</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,86; 38,83</t>
+          <t>36,9; 38,84</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,76; 38,72</t>
+          <t>36,64; 38,48</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>36,94; 38,5</t>
+          <t>36,97; 38,59</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>38,59; 39,76</t>
+          <t>38,62; 39,71</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>37,05; 38,35</t>
+          <t>37,02; 38,35</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>36,73; 38,01</t>
+          <t>36,69; 37,96</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>36,98; 38,13</t>
+          <t>37,01; 38,12</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ39A-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ39A-Estudios-trans_orig.xlsx
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>36,7; 43,68</t>
+          <t>36,91; 43,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>33,68; 41,06</t>
+          <t>33,78; 40,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23,09; 38,49</t>
+          <t>23,13; 38,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>31,93; 40,13</t>
+          <t>32,07; 39,93</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>33,34; 39,84</t>
+          <t>33,45; 40,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,5; 39,67</t>
+          <t>32,36; 39,8</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,8; 43,78</t>
+          <t>35,23; 43,83</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>29,87; 38,88</t>
+          <t>29,7; 38,77</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>36,05; 41,1</t>
+          <t>36,03; 40,93</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>34,42; 39,9</t>
+          <t>34,09; 39,48</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31,98; 40,28</t>
+          <t>32,28; 40,77</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>32,04; 38,41</t>
+          <t>32,2; 38,73</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>39,26; 41,41</t>
+          <t>39,26; 41,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>35,65; 38,09</t>
+          <t>35,75; 38,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36,16; 38,66</t>
+          <t>36,36; 38,71</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36,52; 38,56</t>
+          <t>36,53; 38,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>39,0; 40,79</t>
+          <t>38,97; 40,86</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,36; 39,21</t>
+          <t>36,45; 39,22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,18; 38,81</t>
+          <t>36,26; 38,82</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>37,44; 39,65</t>
+          <t>37,45; 39,71</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>39,37; 40,81</t>
+          <t>39,42; 40,83</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36,44; 38,29</t>
+          <t>36,57; 38,35</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36,61; 38,41</t>
+          <t>36,66; 38,41</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>37,27; 38,81</t>
+          <t>37,28; 38,88</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>36,39; 38,84</t>
+          <t>36,41; 38,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>37,01; 39,86</t>
+          <t>37,03; 39,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>35,31; 38,35</t>
+          <t>35,31; 38,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>35,89; 38,51</t>
+          <t>36,07; 38,48</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>36,0; 38,54</t>
+          <t>35,99; 38,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>37,04; 39,65</t>
+          <t>36,94; 39,63</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>36,2; 38,64</t>
+          <t>36,27; 38,68</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>35,38; 37,57</t>
+          <t>35,18; 37,59</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>36,61; 38,34</t>
+          <t>36,59; 38,41</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>37,36; 39,34</t>
+          <t>37,47; 39,46</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>36,19; 38,1</t>
+          <t>36,23; 38,08</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>36,0; 37,71</t>
+          <t>35,97; 37,65</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>38,57; 40,24</t>
+          <t>38,67; 40,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>36,62; 38,38</t>
+          <t>36,64; 38,43</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>36,14; 38,08</t>
+          <t>35,99; 37,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>36,56; 38,19</t>
+          <t>36,64; 38,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>38,24; 39,72</t>
+          <t>38,17; 39,66</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,9; 38,84</t>
+          <t>36,94; 38,92</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,64; 38,48</t>
+          <t>36,64; 38,54</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>36,97; 38,59</t>
+          <t>36,83; 38,5</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>38,62; 39,71</t>
+          <t>38,64; 39,72</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>37,02; 38,35</t>
+          <t>37,05; 38,35</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>36,69; 37,96</t>
+          <t>36,66; 37,99</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>37,01; 38,12</t>
+          <t>37,01; 38,14</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ39A-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ39A-Estudios-trans_orig.xlsx
@@ -532,7 +532,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -540,7 +540,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -648,42 +648,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>37,09</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>36,47</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>39,9</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>35,78</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>40,1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>37,69</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>31,29</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>36,57</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>37,09</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>36,47</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>39,9</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>35,13</t>
+          <t>35,65</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>35,81</t>
+          <t>35,72</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>36,91; 43,69</t>
+          <t>33,17; 40,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>33,78; 40,73</t>
+          <t>32,22; 39,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23,13; 38,49</t>
+          <t>35,63; 44,16</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>32,07; 39,93</t>
+          <t>30,89; 39,12</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>33,45; 40,05</t>
+          <t>36,87; 43,82</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,36; 39,8</t>
+          <t>33,6; 41,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,23; 43,83</t>
+          <t>22,66; 38,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>29,7; 38,77</t>
+          <t>30,99; 38,78</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>36,03; 40,93</t>
+          <t>35,85; 40,88</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>34,09; 39,48</t>
+          <t>34,2; 39,71</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32,28; 40,77</t>
+          <t>32,22; 40,43</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>32,2; 38,73</t>
+          <t>32,9; 38,15</t>
         </is>
       </c>
     </row>
@@ -788,42 +788,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>39,94</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>37,81</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>37,55</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>38,38</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>40,39</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>36,97</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>37,47</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>37,52</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>39,94</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>37,81</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>37,55</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>38,48</t>
+          <t>37,65</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>38,04</t>
+          <t>38,03</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>39,26; 41,44</t>
+          <t>38,95; 40,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>35,75; 38,06</t>
+          <t>36,47; 39,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36,36; 38,71</t>
+          <t>36,2; 38,78</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36,53; 38,55</t>
+          <t>37,28; 39,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>38,97; 40,86</t>
+          <t>39,27; 41,42</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,45; 39,22</t>
+          <t>35,72; 38,22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,26; 38,82</t>
+          <t>36,31; 38,67</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>37,45; 39,71</t>
+          <t>36,61; 38,65</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>39,42; 40,83</t>
+          <t>39,48; 40,93</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36,57; 38,35</t>
+          <t>36,51; 38,36</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36,66; 38,41</t>
+          <t>36,69; 38,47</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>37,28; 38,88</t>
+          <t>37,35; 38,81</t>
         </is>
       </c>
     </row>
@@ -928,42 +928,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>37,34</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>38,35</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>37,49</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>36,66</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>37,74</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>38,45</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>36,81</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>37,19</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>37,34</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>38,35</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>37,49</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>36,63</t>
+          <t>37,22</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>36,88</t>
+          <t>36,92</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>36,41; 38,79</t>
+          <t>36,1; 38,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>37,03; 39,89</t>
+          <t>36,91; 39,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>35,31; 38,28</t>
+          <t>36,15; 38,62</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>36,07; 38,48</t>
+          <t>35,37; 37,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>35,99; 38,52</t>
+          <t>36,44; 38,86</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>36,94; 39,63</t>
+          <t>37,12; 39,89</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>36,27; 38,68</t>
+          <t>35,21; 38,34</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>35,18; 37,59</t>
+          <t>35,68; 38,46</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>36,59; 38,41</t>
+          <t>36,64; 38,33</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>37,47; 39,46</t>
+          <t>37,38; 39,27</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>36,23; 38,08</t>
+          <t>36,21; 38,12</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>35,97; 37,65</t>
+          <t>36,06; 37,71</t>
         </is>
       </c>
     </row>
@@ -1068,42 +1068,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>38,96</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>37,9</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>37,65</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>37,72</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>39,46</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>37,51</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>37,03</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>37,37</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>38,96</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>37,9</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>37,65</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>37,73</t>
+          <t>37,42</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>37,57</t>
+          <t>37,58</t>
         </is>
       </c>
     </row>
@@ -1136,47 +1136,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>38,67; 40,31</t>
+          <t>38,13; 39,72</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>36,64; 38,43</t>
+          <t>36,86; 38,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>35,99; 37,95</t>
+          <t>36,76; 38,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>36,64; 38,21</t>
+          <t>36,86; 38,45</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>38,17; 39,66</t>
+          <t>38,55; 40,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,94; 38,92</t>
+          <t>36,54; 38,37</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,64; 38,54</t>
+          <t>36,0; 37,93</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>36,83; 38,5</t>
+          <t>36,63; 38,18</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>38,64; 39,72</t>
+          <t>38,59; 39,76</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1186,12 +1186,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>36,66; 37,99</t>
+          <t>36,73; 38,01</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>37,01; 38,14</t>
+          <t>36,99; 38,14</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ39A-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ39A-Estudios-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +140,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -526,7 +531,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adulto según el número de horas que trabaja habitualmente a la semana (tasa de respuesta: 97,26%)</t>
+          <t>Número medio de horas a la semana que la persona entrevistada trabaja habitualmente (tasa de respuesta: 97,26%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -646,419 +651,271 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>37,09</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>36,47</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>39,9</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>35,78</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>40,1</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>37,69</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>31,29</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>35,65</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>38,54</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>37,16</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>36,62</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>35,72</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>37.09396758265925</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>36.47011319982632</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>39.89700043312628</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>35.7773195451013</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>40.10266911789832</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>37.68847241141282</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>31.29213119224931</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>35.64985713694561</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>38.54294640228534</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>37.15561857435561</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>36.6241989907933</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>35.71500874148046</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>33,17; 40,0</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>32,22; 39,79</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>35,63; 44,16</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>30,89; 39,12</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>36,87; 43,82</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>33,6; 41,0</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>22,66; 38,19</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>30,99; 38,78</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>35,85; 40,88</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>34,2; 39,71</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>32,22; 40,43</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>32,9; 38,15</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>33.16997081313598</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>32.21842909214599</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>35.63382062349093</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>30.88734571154318</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>36.87227249409435</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>33.59917293523158</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>22.6625042843051</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>30.98994321172385</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>35.84799187244835</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>34.19682073406985</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>32.22146542846875</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>32.8957006487347</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>40.0033461503797</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>39.78858673843349</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>44.16048561021242</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>39.12021578108193</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>43.82001267082146</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>41.00337235824424</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>38.19039194196404</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>38.77830307313449</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>40.87816215634344</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>39.7059216301061</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>40.42899848021194</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>38.15179020024758</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>39,94</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>37,81</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>37,55</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>38,38</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>40,39</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>36,97</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>37,47</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>37,65</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>40,15</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>37,41</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>37,51</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>38,03</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>38,95; 40,87</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>36,47; 39,32</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>36,2; 38,78</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>37,28; 39,55</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>39,27; 41,42</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>35,72; 38,22</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>36,31; 38,67</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>36,61; 38,65</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>39,48; 40,93</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>36,51; 38,36</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>36,69; 38,47</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>37,35; 38,81</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>39.93519289881971</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>37.80863704913742</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>37.54988584568587</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>38.37725897121414</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>40.39386047153899</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>36.97303791609051</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>37.47462282220236</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>37.64945008850196</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>40.14832685931924</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>37.40879704437123</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>37.51345483555789</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>38.03417581202217</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>37,34</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>38,35</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>37,49</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>36,66</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>37,74</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>38,45</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>36,81</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>37,22</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>37,55</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>38,4</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>37,17</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>36,92</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>38.95334216084885</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>36.47134005511753</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>36.20078677119806</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>37.28260644751992</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>39.27379952811504</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>35.72082010601867</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>36.31356953166922</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>36.61261129474962</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>39.48035392973788</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>36.50992201914572</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>36.6911304695406</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>37.35125840878575</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>36,1; 38,59</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>36,91; 39,75</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>36,15; 38,62</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>35,37; 37,65</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>36,44; 38,86</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>37,12; 39,89</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>35,21; 38,34</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>35,68; 38,46</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>36,64; 38,33</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>37,38; 39,27</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>36,21; 38,12</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>36,06; 37,71</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>40.86964870057112</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>39.31978062685711</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>38.77876409376879</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>39.54629041655105</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>41.42390383701071</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>38.22014184233633</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>38.66534988704498</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>38.65292037564308</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>40.93448835060281</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>38.35784785420103</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>38.4682756179434</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>38.81094194155371</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1066,137 +923,269 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>38,96</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>37,9</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>37,65</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>37,72</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>39,46</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>37,51</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>37,03</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>37,42</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>39,2</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>37,71</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>37,36</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>37,58</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>37.33798328489568</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>38.35263870295296</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>37.49139630328104</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>36.65934888786108</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>37.74191749288725</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>38.4490454595578</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>36.80726927774494</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>37.2238050437396</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>37.55129889926006</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>38.39954428658661</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>37.16679249616972</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>36.92304662272038</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>38,13; 39,72</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>36,86; 38,83</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>36,76; 38,72</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>36,86; 38,45</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>38,55; 40,25</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>36,54; 38,37</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>36,0; 37,93</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>36,63; 38,18</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>38,59; 39,76</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>37,05; 38,35</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>36,73; 38,01</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>36,99; 38,14</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>36.10496629328721</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>36.90742175269929</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>36.15161384331611</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>35.36944526086486</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>36.43565211650924</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>37.12218965444087</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>35.21402292875619</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>35.68455381050154</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>36.64155650481513</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>37.37919408698095</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>36.20833490417745</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>36.06148843725303</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>38.59373909212678</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>39.75302564406513</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>38.62275185658512</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>37.64873267259239</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>38.86164125079745</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>39.8881908905394</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>38.34237467085125</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>38.45520962812689</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>38.33193893153279</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>39.27187183941184</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>38.11555633528194</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>37.71380264219889</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>38.9617474409111</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>37.90219074550711</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>37.65356141937377</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>37.71831790625583</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>39.45980613506651</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>37.51110710414096</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>37.02884430379743</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>37.42077786697383</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>39.20382566576855</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>37.71164114895484</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>37.35608325700891</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>37.57821285251711</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>38.12523773764376</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>36.86293348712334</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>36.75545481731248</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>36.86144092227822</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>38.5533698392418</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>36.54003255877122</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>35.99740135009402</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>36.62692420094989</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>38.58758848846494</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>37.04987776274685</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>36.73002015215267</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>36.98655899429089</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>39.72393772825984</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>38.82678992143239</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>38.72199535822551</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>38.45406183983179</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>40.24687479746343</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>38.37038867402762</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>37.92503434363419</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>38.182825461383</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>39.75863437497605</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>38.35263565720574</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>38.01489188576743</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>38.13930282468861</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1204,14 +1193,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
     <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
